--- a/workspace/Du_Doan_Lam_Phat.xlsx
+++ b/workspace/Du_Doan_Lam_Phat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TNK\Self Develop\toolbox\workspace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FAC695-EB24-4D7A-B99E-FEDB4C065523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475324DE-FCAB-49B3-9101-94B666B333F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28910" yWindow="1630" windowWidth="29020" windowHeight="15820" activeTab="2" xr2:uid="{639E8BC5-1783-4305-AE7B-041856618761}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{639E8BC5-1783-4305-AE7B-041856618761}"/>
   </bookViews>
   <sheets>
     <sheet name="Dự đoán giá nhà" sheetId="3" r:id="rId1"/>
@@ -1294,7 +1294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1317,18 +1317,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1683,18 +1678,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F3B3A0-11C1-4D0E-AD83-41E8B4D1DC3D}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6328125" customWidth="1"/>
-    <col min="4" max="4" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>25</v>
       </c>
@@ -1717,7 +1712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>2025</v>
       </c>
@@ -1740,7 +1735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2026</v>
       </c>
@@ -1764,7 +1759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>2027</v>
       </c>
@@ -1788,7 +1783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2028</v>
       </c>
@@ -1812,7 +1807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>2029</v>
       </c>
@@ -1836,7 +1831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2030</v>
       </c>
@@ -1860,7 +1855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>2031</v>
       </c>
@@ -1884,7 +1879,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2032</v>
       </c>
@@ -1908,7 +1903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2033</v>
       </c>
@@ -1932,7 +1927,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>2034</v>
       </c>
@@ -1956,7 +1951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>2035</v>
       </c>
@@ -1988,7 +1983,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB5FAA3-D215-41FE-9C13-E641F04EDD21}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1997,67 +1992,67 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75AC9DCA-D84B-49FE-B2FF-085A73E4AD6E}">
   <dimension ref="A2:ER50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.36328125" customWidth="1"/>
-    <col min="4" max="4" width="28.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="126.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.90625" customWidth="1"/>
-    <col min="8" max="8" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="75.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.453125" customWidth="1"/>
-    <col min="17" max="17" width="38.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="40.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.7265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="82.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.54296875" customWidth="1"/>
-    <col min="23" max="23" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="31.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="126.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="75.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" customWidth="1"/>
+    <col min="17" max="17" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="82.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5703125" customWidth="1"/>
+    <col min="23" max="23" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9" customWidth="1"/>
-    <col min="27" max="28" width="15.1796875" customWidth="1"/>
-    <col min="29" max="29" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="15.140625" customWidth="1"/>
+    <col min="29" max="29" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="6" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.36328125" customWidth="1"/>
-    <col min="38" max="38" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="76.54296875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="80.54296875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="5.36328125" style="9" customWidth="1"/>
-    <col min="44" max="44" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="47.1796875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="77.81640625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="14.81640625" customWidth="1"/>
-    <col min="53" max="53" width="35.7265625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="38.08984375" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.42578125" customWidth="1"/>
+    <col min="38" max="38" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="76.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="80.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="5.42578125" style="9" customWidth="1"/>
+    <col min="44" max="44" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14.85546875" customWidth="1"/>
+    <col min="53" max="53" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="35" customWidth="1"/>
-    <col min="66" max="66" width="25.90625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="31.6328125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="31.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:148" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:148" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -2215,7 +2210,7 @@
         <f>IF(AP3&lt;&gt;"", "MD-" &amp; COUNTIF($D3:AP3, "&lt;&gt;"), "")</f>
         <v/>
       </c>
-      <c r="AQ2" s="14" t="str">
+      <c r="AQ2" s="12" t="str">
         <f>IF(AQ3&lt;&gt;"", "MD-" &amp; COUNTIF($D3:AQ3, "&lt;&gt;"), "")</f>
         <v>MD-8</v>
       </c>
@@ -2632,7 +2627,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
@@ -2659,7 +2654,7 @@
       <c r="AK3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="AQ3" s="15" t="s">
+      <c r="AQ3" s="13" t="s">
         <v>123</v>
       </c>
       <c r="AX3" s="3" t="s">
@@ -2670,7 +2665,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -2686,10 +2681,10 @@
       <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="3" t="s">
         <v>246</v>
       </c>
       <c r="K4" s="3" t="s">
@@ -2719,49 +2714,49 @@
       <c r="T4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="V4" s="11" t="s">
+      <c r="V4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="W4" s="11" t="s">
+      <c r="W4" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="X4" s="11" t="s">
+      <c r="X4" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="Y4" s="11" t="s">
+      <c r="Y4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Z4" s="11" t="s">
+      <c r="Z4" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="AA4" s="11" t="s">
+      <c r="AA4" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="AB4" s="11" t="s">
+      <c r="AB4" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AC4" s="11" t="s">
+      <c r="AC4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="AD4" s="11" t="s">
+      <c r="AD4" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="AF4" s="11" t="s">
+      <c r="AF4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="AG4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AH4" s="11" t="s">
+      <c r="AH4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AI4" s="11" t="s">
+      <c r="AI4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AK4" s="11" t="s">
+      <c r="AK4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="AL4" s="11" t="s">
+      <c r="AL4" s="3" t="s">
         <v>120</v>
       </c>
       <c r="AM4" s="3" t="s">
@@ -2791,10 +2786,10 @@
       <c r="AV4" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="AX4" s="11" t="s">
+      <c r="AX4" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="AY4" s="11" t="s">
+      <c r="AY4" s="3" t="s">
         <v>250</v>
       </c>
       <c r="AZ4" s="3" t="s">
@@ -2838,7 +2833,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str" cm="1">
         <f t="array" ref="A5:A14">TRANSPOSE(_xlfn.UNIQUE(_xlfn._xlws.FILTER($B2:$AAC2, $B2:$AAC2&lt;&gt;"")))</f>
         <v>MD-1</v>
@@ -3014,7 +3009,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
         <v>MD-2</v>
       </c>
@@ -3033,7 +3028,7 @@
       <c r="H6" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="11" t="s">
         <v>171</v>
       </c>
       <c r="K6" s="8">
@@ -3188,7 +3183,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="7" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
         <v>MD-3</v>
       </c>
@@ -3205,7 +3200,7 @@
       <c r="H7" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="11" t="s">
         <v>172</v>
       </c>
       <c r="K7" s="8">
@@ -3360,7 +3355,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
         <v>MD-4</v>
       </c>
@@ -3370,7 +3365,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="2" t="s">
         <v>249</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -3520,7 +3515,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="9" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
         <v>MD-5</v>
       </c>
@@ -3530,7 +3525,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="2" t="s">
         <v>249</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -3680,7 +3675,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="10" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
         <v>MD-6</v>
       </c>
@@ -3826,7 +3821,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="11" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
         <v>MD-7</v>
       </c>
@@ -3964,7 +3959,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="12" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
         <v>MD-8</v>
       </c>
@@ -4102,7 +4097,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="13" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
         <v>MD-9</v>
       </c>
@@ -4240,7 +4235,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="14" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
         <v>MD-10</v>
       </c>
@@ -4378,7 +4373,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="15" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="D15" s="2"/>
@@ -4502,7 +4497,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="16" spans="1:148" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:148" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="D16" s="2"/>
@@ -4566,7 +4561,7 @@
       <c r="AM16" s="2"/>
       <c r="AN16" s="2"/>
       <c r="AO16" s="2"/>
-      <c r="AQ16" s="16" t="str">
+      <c r="AQ16" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4621,7 +4616,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="17" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="D17" s="2"/>
@@ -4685,7 +4680,7 @@
       <c r="AM17" s="2"/>
       <c r="AN17" s="2"/>
       <c r="AO17" s="2"/>
-      <c r="AQ17" s="16" t="str">
+      <c r="AQ17" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4740,7 +4735,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="18" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="D18" s="2"/>
@@ -4804,7 +4799,7 @@
       <c r="AM18" s="2"/>
       <c r="AN18" s="2"/>
       <c r="AO18" s="2"/>
-      <c r="AQ18" s="16" t="str">
+      <c r="AQ18" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4859,7 +4854,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="19" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="D19" s="2"/>
@@ -4906,7 +4901,7 @@
       <c r="AM19" s="2"/>
       <c r="AN19" s="2"/>
       <c r="AO19" s="2"/>
-      <c r="AQ19" s="16" t="str">
+      <c r="AQ19" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4961,7 +4956,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="D20" s="2"/>
@@ -5008,7 +5003,7 @@
       <c r="AM20" s="2"/>
       <c r="AN20" s="2"/>
       <c r="AO20" s="2"/>
-      <c r="AQ20" s="16" t="str">
+      <c r="AQ20" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5063,7 +5058,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="21" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -5090,7 +5085,7 @@
       <c r="AD21" s="8">
         <v>1.5</v>
       </c>
-      <c r="AQ21" s="16" t="str">
+      <c r="AQ21" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5145,7 +5140,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="22" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -5162,7 +5157,7 @@
       <c r="AB22" s="2"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="2"/>
-      <c r="AQ22" s="16" t="str">
+      <c r="AQ22" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5217,7 +5212,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="23" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -5234,7 +5229,7 @@
       <c r="AB23" s="2"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="2"/>
-      <c r="AQ23" s="16" t="str">
+      <c r="AQ23" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5289,7 +5284,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="24" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -5306,7 +5301,7 @@
       <c r="AB24" s="2"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="2"/>
-      <c r="AQ24" s="16" t="str">
+      <c r="AQ24" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5361,7 +5356,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="25" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -5378,7 +5373,7 @@
       <c r="AB25" s="2"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="2"/>
-      <c r="AQ25" s="16" t="str">
+      <c r="AQ25" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5433,7 +5428,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="26" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -5450,7 +5445,7 @@
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="2"/>
-      <c r="AQ26" s="16" t="str">
+      <c r="AQ26" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5505,7 +5500,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="27" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -5522,7 +5517,7 @@
       <c r="AB27" s="2"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="2"/>
-      <c r="AQ27" s="16" t="str">
+      <c r="AQ27" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5577,7 +5572,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="28" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -5594,7 +5589,7 @@
       <c r="AB28" s="2"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="2"/>
-      <c r="AQ28" s="16" t="str">
+      <c r="AQ28" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5649,7 +5644,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="29" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -5666,7 +5661,7 @@
       <c r="AB29" s="2"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="2"/>
-      <c r="AQ29" s="16" t="str">
+      <c r="AQ29" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5721,7 +5716,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="30" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:67" x14ac:dyDescent="0.25">
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -5738,7 +5733,7 @@
       <c r="AB30" s="2"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="2"/>
-      <c r="AQ30" s="16" t="str">
+      <c r="AQ30" s="9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5793,7 +5788,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="31" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:67" x14ac:dyDescent="0.25">
       <c r="AX31" s="2">
         <v>27</v>
       </c>
@@ -5845,7 +5840,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="32" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:67" x14ac:dyDescent="0.25">
       <c r="AX32" s="2">
         <v>28</v>
       </c>
@@ -5897,7 +5892,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="33" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="33" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX33" s="2">
         <v>29</v>
       </c>
@@ -5949,7 +5944,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="34" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="34" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX34" s="2">
         <v>30</v>
       </c>
@@ -6001,7 +5996,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="35" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="35" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX35" s="2">
         <v>31</v>
       </c>
@@ -6053,7 +6048,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="36" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="36" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX36" s="2">
         <v>32</v>
       </c>
@@ -6087,7 +6082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="37" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX37" s="2">
         <v>33</v>
       </c>
@@ -6121,7 +6116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="38" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX38" s="2">
         <v>34</v>
       </c>
@@ -6155,7 +6150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="39" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX39" s="2">
         <v>35</v>
       </c>
@@ -6189,7 +6184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="40" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX40" s="2">
         <v>36</v>
       </c>
@@ -6223,7 +6218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="41" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX41" s="2">
         <v>37</v>
       </c>
@@ -6257,7 +6252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="42" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX42" s="2">
         <v>38</v>
       </c>
@@ -6291,7 +6286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="43" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX43" s="2">
         <v>39</v>
       </c>
@@ -6325,7 +6320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="44" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX44" s="2"/>
       <c r="AY44" s="2"/>
       <c r="AZ44" s="2"/>
@@ -6343,7 +6338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="45" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX45" s="2"/>
       <c r="AY45" s="2"/>
       <c r="AZ45" s="2"/>
@@ -6361,7 +6356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="46" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX46" s="2"/>
       <c r="AY46" s="2"/>
       <c r="AZ46" s="2"/>
@@ -6379,7 +6374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="47" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX47" s="2"/>
       <c r="AY47" s="2"/>
       <c r="AZ47" s="2"/>
@@ -6397,7 +6392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="50:67" x14ac:dyDescent="0.35">
+    <row r="48" spans="50:67" x14ac:dyDescent="0.25">
       <c r="AX48" s="2"/>
       <c r="AY48" s="2"/>
       <c r="AZ48" s="2"/>
@@ -6415,7 +6410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="50:59" x14ac:dyDescent="0.35">
+    <row r="49" spans="50:59" x14ac:dyDescent="0.25">
       <c r="AX49" s="2"/>
       <c r="AY49" s="2"/>
       <c r="AZ49" s="2"/>
@@ -6433,7 +6428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="50:59" x14ac:dyDescent="0.35">
+    <row r="50" spans="50:59" x14ac:dyDescent="0.25">
       <c r="AX50" s="2"/>
       <c r="AY50" s="2"/>
       <c r="AZ50" s="2"/>
@@ -6474,4 +6469,10 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{189c1a2f-03d3-4788-bafa-4d9775e75610}" enabled="1" method="Privileged" siteId="{c19239e5-1337-436d-800a-1b4283c280dd}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>